--- a/app/data/employees.xlsx
+++ b/app/data/employees.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data Section" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,38 +453,38 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>M.Umair Saeed</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>03401975074</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Press &amp; Finishing</t>
+          <t>role</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>On Duty</t>
+          <t>status</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>current_task</t>
         </is>
       </c>
     </row>
@@ -511,10 +511,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>On Duty</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>On Task</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -539,10 +543,14 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On Duty</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>On Task</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
